--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -386,7 +386,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="str">
-        <v>multi-venue - Sales Summary - 2025-06-01/2025-06-28</v>
+        <v>multi-venue - Sales Summary - 2025-06-01/2025-06-29</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -414,139 +414,139 @@
         <v>#001 Florida Mall Orlando FL</v>
       </c>
       <c r="B3" t="str">
-        <v>78,898.16</v>
+        <v>82,361.73</v>
       </c>
       <c r="C3" t="str">
-        <v>78,845.76</v>
+        <v>82,309.33</v>
       </c>
       <c r="D3" t="str">
         <v>52.40</v>
       </c>
       <c r="E3" t="str">
-        <v>581.08</v>
+        <v>604.44</v>
       </c>
       <c r="F3" t="str">
-        <v>5,277</v>
+        <v>5,506</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
-        <v>#002 American Dream Mall NJ</v>
+        <v>#006 Aventura, FL</v>
       </c>
       <c r="B4" t="str">
-        <v>71,827.36</v>
+        <v>31,376.96</v>
       </c>
       <c r="C4" t="str">
-        <v>71,583.10</v>
+        <v>31,299.13</v>
       </c>
       <c r="D4" t="str">
-        <v>244.26</v>
+        <v>77.83</v>
       </c>
       <c r="E4" t="str">
-        <v>960.03</v>
+        <v>287.21</v>
       </c>
       <c r="F4" t="str">
-        <v>4,442</v>
+        <v>1,817</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
-        <v>#005 Vineland Orlando FL</v>
+        <v>#002 American Dream Mall NJ</v>
       </c>
       <c r="B5" t="str">
-        <v>30,207.38</v>
+        <v>74,975.26</v>
       </c>
       <c r="C5" t="str">
-        <v>30,164.45</v>
+        <v>74,722.74</v>
       </c>
       <c r="D5" t="str">
-        <v>42.93</v>
+        <v>252.52</v>
       </c>
       <c r="E5" t="str">
-        <v>226.97</v>
+        <v>1,038.44</v>
       </c>
       <c r="F5" t="str">
-        <v>2,491</v>
+        <v>4,640</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
-        <v>#004 Weston Town Center FL</v>
+        <v>#003 Sawgrass Mills Mall FL</v>
       </c>
       <c r="B6" t="str">
-        <v>65,857.82</v>
+        <v>101,310.60</v>
       </c>
       <c r="C6" t="str">
-        <v>65,795.43</v>
+        <v>101,142.68</v>
       </c>
       <c r="D6" t="str">
-        <v>62.39</v>
+        <v>167.92</v>
       </c>
       <c r="E6" t="str">
-        <v>928.67</v>
+        <v>1,035.83</v>
       </c>
       <c r="F6" t="str">
-        <v>4,030</v>
+        <v>7,012</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
-        <v>Lucciano's Vineland 2026</v>
+        <v>#004 Weston Town Center FL</v>
       </c>
       <c r="B7" t="str">
-        <v>0.00</v>
+        <v>68,835.28</v>
       </c>
       <c r="C7" t="str">
-        <v>0.00</v>
+        <v>68,769.48</v>
       </c>
       <c r="D7" t="str">
-        <v>0.00</v>
+        <v>65.80</v>
       </c>
       <c r="E7" t="str">
-        <v>0.00</v>
+        <v>980.40</v>
       </c>
       <c r="F7" t="str">
-        <v>0</v>
+        <v>4,203</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
-        <v>#003 Sawgrass Mills Mall FL</v>
+        <v>#005 Vineland Orlando FL</v>
       </c>
       <c r="B8" t="str">
-        <v>97,388.88</v>
+        <v>30,733.88</v>
       </c>
       <c r="C8" t="str">
-        <v>97,227.74</v>
+        <v>30,690.95</v>
       </c>
       <c r="D8" t="str">
-        <v>161.14</v>
+        <v>42.93</v>
       </c>
       <c r="E8" t="str">
-        <v>954.43</v>
+        <v>241.65</v>
       </c>
       <c r="F8" t="str">
-        <v>6,757</v>
+        <v>2,540</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
-        <v>#006 Aventura, FL</v>
+        <v>Lucciano's Vineland 2026</v>
       </c>
       <c r="B9" t="str">
-        <v>29,934.48</v>
+        <v>0.00</v>
       </c>
       <c r="C9" t="str">
-        <v>29,856.65</v>
+        <v>0.00</v>
       </c>
       <c r="D9" t="str">
-        <v>77.83</v>
+        <v>0.00</v>
       </c>
       <c r="E9" t="str">
-        <v>280.96</v>
+        <v>0.00</v>
       </c>
       <c r="F9" t="str">
-        <v>1,727</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -554,19 +554,19 @@
         <v>REPORT SUMMARY (7 entries)</v>
       </c>
       <c r="B10" t="str">
-        <v>374,114.08</v>
+        <v>389,593.71</v>
       </c>
       <c r="C10" t="str">
-        <v>373,473.13</v>
+        <v>388,934.31</v>
       </c>
       <c r="D10" t="str">
-        <v>640.95</v>
+        <v>659.40</v>
       </c>
       <c r="E10" t="str">
-        <v>3,932.14</v>
+        <v>4,187.97</v>
       </c>
       <c r="F10" t="str">
-        <v>24,724</v>
+        <v>25,718</v>
       </c>
     </row>
   </sheetData>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -386,7 +386,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="str">
-        <v>multi-venue - Sales Summary - 2025-06-01/2025-06-29</v>
+        <v>multi-venue - Sales Summary - 2025-06-01/2025-06-30</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -411,82 +411,82 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
-        <v>#001 Florida Mall Orlando FL</v>
+        <v>#003 Sawgrass Mills Mall FL</v>
       </c>
       <c r="B3" t="str">
-        <v>82,361.73</v>
+        <v>103,974.81</v>
       </c>
       <c r="C3" t="str">
-        <v>82,309.33</v>
+        <v>103,779.93</v>
       </c>
       <c r="D3" t="str">
-        <v>52.40</v>
+        <v>194.88</v>
       </c>
       <c r="E3" t="str">
-        <v>604.44</v>
+        <v>1,068.59</v>
       </c>
       <c r="F3" t="str">
-        <v>5,506</v>
+        <v>7,204</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
-        <v>#006 Aventura, FL</v>
+        <v>#001 Florida Mall Orlando FL</v>
       </c>
       <c r="B4" t="str">
-        <v>31,376.96</v>
+        <v>84,676.38</v>
       </c>
       <c r="C4" t="str">
-        <v>31,299.13</v>
+        <v>84,623.98</v>
       </c>
       <c r="D4" t="str">
-        <v>77.83</v>
+        <v>52.40</v>
       </c>
       <c r="E4" t="str">
-        <v>287.21</v>
+        <v>613.13</v>
       </c>
       <c r="F4" t="str">
-        <v>1,817</v>
+        <v>5,660</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
-        <v>#002 American Dream Mall NJ</v>
+        <v>Lucciano's Vineland 2026</v>
       </c>
       <c r="B5" t="str">
-        <v>74,975.26</v>
+        <v>0.00</v>
       </c>
       <c r="C5" t="str">
-        <v>74,722.74</v>
+        <v>0.00</v>
       </c>
       <c r="D5" t="str">
-        <v>252.52</v>
+        <v>0.00</v>
       </c>
       <c r="E5" t="str">
-        <v>1,038.44</v>
+        <v>0.00</v>
       </c>
       <c r="F5" t="str">
-        <v>4,640</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
-        <v>#003 Sawgrass Mills Mall FL</v>
+        <v>#005 Vineland Orlando FL</v>
       </c>
       <c r="B6" t="str">
-        <v>101,310.60</v>
+        <v>31,286.85</v>
       </c>
       <c r="C6" t="str">
-        <v>101,142.68</v>
+        <v>31,243.17</v>
       </c>
       <c r="D6" t="str">
-        <v>167.92</v>
+        <v>43.68</v>
       </c>
       <c r="E6" t="str">
-        <v>1,035.83</v>
+        <v>241.65</v>
       </c>
       <c r="F6" t="str">
-        <v>7,012</v>
+        <v>2,587</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -494,10 +494,10 @@
         <v>#004 Weston Town Center FL</v>
       </c>
       <c r="B7" t="str">
-        <v>68,835.28</v>
+        <v>71,253.88</v>
       </c>
       <c r="C7" t="str">
-        <v>68,769.48</v>
+        <v>71,188.08</v>
       </c>
       <c r="D7" t="str">
         <v>65.80</v>
@@ -506,47 +506,47 @@
         <v>980.40</v>
       </c>
       <c r="F7" t="str">
-        <v>4,203</v>
+        <v>4,283</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
-        <v>#005 Vineland Orlando FL</v>
+        <v>#006 Aventura, FL</v>
       </c>
       <c r="B8" t="str">
-        <v>30,733.88</v>
+        <v>32,858.08</v>
       </c>
       <c r="C8" t="str">
-        <v>30,690.95</v>
+        <v>32,779.92</v>
       </c>
       <c r="D8" t="str">
-        <v>42.93</v>
+        <v>78.16</v>
       </c>
       <c r="E8" t="str">
-        <v>241.65</v>
+        <v>287.21</v>
       </c>
       <c r="F8" t="str">
-        <v>2,540</v>
+        <v>1,860</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
-        <v>Lucciano's Vineland 2026</v>
+        <v>#002 American Dream Mall NJ</v>
       </c>
       <c r="B9" t="str">
-        <v>0.00</v>
+        <v>76,925.55</v>
       </c>
       <c r="C9" t="str">
-        <v>0.00</v>
+        <v>76,666.51</v>
       </c>
       <c r="D9" t="str">
-        <v>0.00</v>
+        <v>259.04</v>
       </c>
       <c r="E9" t="str">
-        <v>0.00</v>
+        <v>1,074.05</v>
       </c>
       <c r="F9" t="str">
-        <v>0</v>
+        <v>4,765</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -554,19 +554,19 @@
         <v>REPORT SUMMARY (7 entries)</v>
       </c>
       <c r="B10" t="str">
-        <v>389,593.71</v>
+        <v>400,975.55</v>
       </c>
       <c r="C10" t="str">
-        <v>388,934.31</v>
+        <v>400,281.59</v>
       </c>
       <c r="D10" t="str">
-        <v>659.40</v>
+        <v>693.96</v>
       </c>
       <c r="E10" t="str">
-        <v>4,187.97</v>
+        <v>4,265.03</v>
       </c>
       <c r="F10" t="str">
-        <v>25,718</v>
+        <v>26,359</v>
       </c>
     </row>
   </sheetData>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -1,29 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="sheet1" state="visible" r:id="rId3"/>
+    <sheet name="Sales Summary" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts x14ac:knownFonts="1" count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <color theme="1"/>
-      <family val="2"/>
+      <sz val="11"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -42,21 +47,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -135,7 +199,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -170,7 +233,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -205,16 +267,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -336,241 +402,214 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="str">
-        <v>multi-venue - Sales Summary - 2025-06-01/2025-06-30</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="str">
-        <v>"Venue Name"</v>
-      </c>
-      <c r="B2" t="str">
-        <v>"Gross Sales"</v>
-      </c>
-      <c r="C2" t="str">
-        <v>"Net Sales"</v>
-      </c>
-      <c r="D2" t="str">
-        <v>"Discounts"</v>
-      </c>
-      <c r="E2" t="str">
-        <v>"Voids"</v>
-      </c>
-      <c r="F2" t="str">
-        <v>"Bill Count"</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="str">
-        <v>#003 Sawgrass Mills Mall FL</v>
-      </c>
-      <c r="B3" t="str">
-        <v>103,974.81</v>
-      </c>
-      <c r="C3" t="str">
-        <v>103,779.93</v>
-      </c>
-      <c r="D3" t="str">
-        <v>194.88</v>
-      </c>
-      <c r="E3" t="str">
-        <v>1,068.59</v>
-      </c>
-      <c r="F3" t="str">
-        <v>7,204</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" t="str">
-        <v>#001 Florida Mall Orlando FL</v>
-      </c>
-      <c r="B4" t="str">
-        <v>84,676.38</v>
-      </c>
-      <c r="C4" t="str">
-        <v>84,623.98</v>
-      </c>
-      <c r="D4" t="str">
-        <v>52.40</v>
-      </c>
-      <c r="E4" t="str">
-        <v>613.13</v>
-      </c>
-      <c r="F4" t="str">
-        <v>5,660</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" t="str">
-        <v>Lucciano's Vineland 2026</v>
-      </c>
-      <c r="B5" t="str">
-        <v>0.00</v>
-      </c>
-      <c r="C5" t="str">
-        <v>0.00</v>
-      </c>
-      <c r="D5" t="str">
-        <v>0.00</v>
-      </c>
-      <c r="E5" t="str">
-        <v>0.00</v>
-      </c>
-      <c r="F5" t="str">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" t="str">
-        <v>#005 Vineland Orlando FL</v>
-      </c>
-      <c r="B6" t="str">
-        <v>31,286.85</v>
-      </c>
-      <c r="C6" t="str">
-        <v>31,243.17</v>
-      </c>
-      <c r="D6" t="str">
-        <v>43.68</v>
-      </c>
-      <c r="E6" t="str">
-        <v>241.65</v>
-      </c>
-      <c r="F6" t="str">
-        <v>2,587</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" t="str">
-        <v>#004 Weston Town Center FL</v>
-      </c>
-      <c r="B7" t="str">
-        <v>71,253.88</v>
-      </c>
-      <c r="C7" t="str">
-        <v>71,188.08</v>
-      </c>
-      <c r="D7" t="str">
-        <v>65.80</v>
-      </c>
-      <c r="E7" t="str">
-        <v>980.40</v>
-      </c>
-      <c r="F7" t="str">
-        <v>4,283</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" t="str">
-        <v>#006 Aventura, FL</v>
-      </c>
-      <c r="B8" t="str">
-        <v>32,858.08</v>
-      </c>
-      <c r="C8" t="str">
-        <v>32,779.92</v>
-      </c>
-      <c r="D8" t="str">
-        <v>78.16</v>
-      </c>
-      <c r="E8" t="str">
-        <v>287.21</v>
-      </c>
-      <c r="F8" t="str">
-        <v>1,860</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" t="str">
-        <v>#002 American Dream Mall NJ</v>
-      </c>
-      <c r="B9" t="str">
-        <v>76,925.55</v>
-      </c>
-      <c r="C9" t="str">
-        <v>76,666.51</v>
-      </c>
-      <c r="D9" t="str">
-        <v>259.04</v>
-      </c>
-      <c r="E9" t="str">
-        <v>1,074.05</v>
-      </c>
-      <c r="F9" t="str">
-        <v>4,765</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" t="str">
-        <v>REPORT SUMMARY (7 entries)</v>
-      </c>
-      <c r="B10" t="str">
-        <v>400,975.55</v>
-      </c>
-      <c r="C10" t="str">
-        <v>400,281.59</v>
-      </c>
-      <c r="D10" t="str">
-        <v>693.96</v>
-      </c>
-      <c r="E10" t="str">
-        <v>4,265.03</v>
-      </c>
-      <c r="F10" t="str">
-        <v>26,359</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Venue Name</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Gross Sales</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Net Sales</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Discounts</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Voids</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Bill Count</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>#001 Florida Mall Orlando FL</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2163.49</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2163.49</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>#002 American Dream Mall NJ</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2649.09</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2649.09</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>#003 Sawgrass Mills Mall FL</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2285.69</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2285.69</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>#004 Weston Town Center FL</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1361.48</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1361.48</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>#005 Vineland Orlando FL</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>524.25</v>
+      </c>
+      <c r="C7" t="n">
+        <v>524.25</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>#006 Aventura, FL</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>979.86</v>
+      </c>
+      <c r="C8" t="n">
+        <v>979.86</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>REPORT SUMMARY (6 entries)</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>9963.860000000001</v>
+      </c>
+      <c r="C9" t="n">
+        <v>9963.860000000001</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-01</t>
+          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-02</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2163.49</v>
+        <v>4232.63</v>
       </c>
       <c r="C3" t="n">
-        <v>2163.49</v>
+        <v>4232.63</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2649.09</v>
+        <v>5052.89</v>
       </c>
       <c r="C4" t="n">
-        <v>2649.09</v>
+        <v>5052.89</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2285.69</v>
+        <v>4849.28</v>
       </c>
       <c r="C5" t="n">
-        <v>2285.69</v>
+        <v>4849.28</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1361.48</v>
+        <v>2652.37</v>
       </c>
       <c r="C6" t="n">
-        <v>1361.48</v>
+        <v>2652.37</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>524.25</v>
+        <v>1569.54</v>
       </c>
       <c r="C7" t="n">
-        <v>524.25</v>
+        <v>1569.54</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>979.86</v>
+        <v>1351.17</v>
       </c>
       <c r="C8" t="n">
-        <v>979.86</v>
+        <v>1351.17</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9963.860000000001</v>
+        <v>19707.88</v>
       </c>
       <c r="C9" t="n">
-        <v>9963.860000000001</v>
+        <v>19707.88</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-02</t>
+          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-03</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4232.63</v>
+        <v>7196.82</v>
       </c>
       <c r="C3" t="n">
-        <v>4232.63</v>
+        <v>7196.82</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5052.89</v>
+        <v>7360.51</v>
       </c>
       <c r="C4" t="n">
-        <v>5052.89</v>
+        <v>7360.51</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4849.28</v>
+        <v>8184.66</v>
       </c>
       <c r="C5" t="n">
-        <v>4849.28</v>
+        <v>8184.66</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2652.37</v>
+        <v>4838.03</v>
       </c>
       <c r="C6" t="n">
-        <v>2652.37</v>
+        <v>4838.03</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1569.54</v>
+        <v>2894.44</v>
       </c>
       <c r="C7" t="n">
-        <v>1569.54</v>
+        <v>2894.44</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1351.17</v>
+        <v>2122.24</v>
       </c>
       <c r="C8" t="n">
-        <v>1351.17</v>
+        <v>2122.24</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19707.88</v>
+        <v>32596.7</v>
       </c>
       <c r="C9" t="n">
-        <v>19707.88</v>
+        <v>32596.7</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-03</t>
+          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-04</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7196.82</v>
+        <v>10175.56</v>
       </c>
       <c r="C3" t="n">
-        <v>7196.82</v>
+        <v>10175.56</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7360.51</v>
+        <v>10206.9</v>
       </c>
       <c r="C4" t="n">
-        <v>7360.51</v>
+        <v>10206.9</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8184.66</v>
+        <v>12475.3</v>
       </c>
       <c r="C5" t="n">
-        <v>8184.66</v>
+        <v>12475.3</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4838.03</v>
+        <v>8770.120000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>4838.03</v>
+        <v>8770.120000000001</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2894.44</v>
+        <v>4798.17</v>
       </c>
       <c r="C7" t="n">
-        <v>2894.44</v>
+        <v>4798.17</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2122.24</v>
+        <v>2905.8</v>
       </c>
       <c r="C8" t="n">
-        <v>2122.24</v>
+        <v>2905.8</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>32596.7</v>
+        <v>49331.85</v>
       </c>
       <c r="C9" t="n">
-        <v>32596.7</v>
+        <v>49331.85</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-04</t>
+          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-05</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10175.56</v>
+        <v>15264.37</v>
       </c>
       <c r="C3" t="n">
-        <v>10175.56</v>
+        <v>15264.37</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10206.9</v>
+        <v>14928.56</v>
       </c>
       <c r="C4" t="n">
-        <v>10206.9</v>
+        <v>14928.56</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12475.3</v>
+        <v>17517.46</v>
       </c>
       <c r="C5" t="n">
-        <v>12475.3</v>
+        <v>17517.46</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8770.120000000001</v>
+        <v>12646.07</v>
       </c>
       <c r="C6" t="n">
-        <v>8770.120000000001</v>
+        <v>12646.07</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4798.17</v>
+        <v>6057.04</v>
       </c>
       <c r="C7" t="n">
-        <v>4798.17</v>
+        <v>6057.04</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2905.8</v>
+        <v>4646.51</v>
       </c>
       <c r="C8" t="n">
-        <v>2905.8</v>
+        <v>4646.51</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>49331.85</v>
+        <v>71060.00999999999</v>
       </c>
       <c r="C9" t="n">
-        <v>49331.85</v>
+        <v>71060.00999999999</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-05</t>
+          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-06</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15264.37</v>
+        <v>19528.37</v>
       </c>
       <c r="C3" t="n">
-        <v>15264.37</v>
+        <v>19528.37</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14928.56</v>
+        <v>18750.18</v>
       </c>
       <c r="C4" t="n">
-        <v>14928.56</v>
+        <v>18750.18</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17517.46</v>
+        <v>21187.75</v>
       </c>
       <c r="C5" t="n">
-        <v>17517.46</v>
+        <v>21187.75</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12646.07</v>
+        <v>15224.79</v>
       </c>
       <c r="C6" t="n">
-        <v>12646.07</v>
+        <v>15224.79</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6057.04</v>
+        <v>6816.85</v>
       </c>
       <c r="C7" t="n">
-        <v>6057.04</v>
+        <v>6816.85</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4646.51</v>
+        <v>5724.93</v>
       </c>
       <c r="C8" t="n">
-        <v>4646.51</v>
+        <v>5724.93</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>71060.00999999999</v>
+        <v>87232.87</v>
       </c>
       <c r="C9" t="n">
-        <v>71060.00999999999</v>
+        <v>87232.87</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-06</t>
+          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-07</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19528.37</v>
+        <v>22012.19</v>
       </c>
       <c r="C3" t="n">
-        <v>19528.37</v>
+        <v>22012.19</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18750.18</v>
+        <v>20786.06</v>
       </c>
       <c r="C4" t="n">
-        <v>18750.18</v>
+        <v>20786.06</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21187.75</v>
+        <v>24047.16</v>
       </c>
       <c r="C5" t="n">
-        <v>21187.75</v>
+        <v>24047.16</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15224.79</v>
+        <v>16821.92</v>
       </c>
       <c r="C6" t="n">
-        <v>15224.79</v>
+        <v>16821.92</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6816.85</v>
+        <v>6998.6</v>
       </c>
       <c r="C7" t="n">
-        <v>6816.85</v>
+        <v>6998.6</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5724.93</v>
+        <v>6275.93</v>
       </c>
       <c r="C8" t="n">
-        <v>5724.93</v>
+        <v>6275.93</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>87232.87</v>
+        <v>96941.86000000002</v>
       </c>
       <c r="C9" t="n">
-        <v>87232.87</v>
+        <v>96941.86000000002</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-07</t>
+          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-08</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22012.19</v>
+        <v>24095.69</v>
       </c>
       <c r="C3" t="n">
-        <v>22012.19</v>
+        <v>24095.69</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20786.06</v>
+        <v>23971.62</v>
       </c>
       <c r="C4" t="n">
-        <v>20786.06</v>
+        <v>23971.62</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24047.16</v>
+        <v>26615.11</v>
       </c>
       <c r="C5" t="n">
-        <v>24047.16</v>
+        <v>26615.11</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16821.92</v>
+        <v>18623.36</v>
       </c>
       <c r="C6" t="n">
-        <v>16821.92</v>
+        <v>18623.36</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6998.6</v>
+        <v>7141.91</v>
       </c>
       <c r="C7" t="n">
-        <v>6998.6</v>
+        <v>7141.91</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6275.93</v>
+        <v>6864.06</v>
       </c>
       <c r="C8" t="n">
-        <v>6275.93</v>
+        <v>6864.06</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>96941.86000000002</v>
+        <v>107311.75</v>
       </c>
       <c r="C9" t="n">
-        <v>96941.86000000002</v>
+        <v>107311.75</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-08</t>
+          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-09</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24095.69</v>
+        <v>26471.04</v>
       </c>
       <c r="C3" t="n">
-        <v>24095.69</v>
+        <v>26471.04</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23971.62</v>
+        <v>25857.53</v>
       </c>
       <c r="C4" t="n">
-        <v>23971.62</v>
+        <v>25857.53</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26615.11</v>
+        <v>29461.95</v>
       </c>
       <c r="C5" t="n">
-        <v>26615.11</v>
+        <v>29461.95</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18623.36</v>
+        <v>20296.36</v>
       </c>
       <c r="C6" t="n">
-        <v>18623.36</v>
+        <v>20296.36</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7141.91</v>
+        <v>7523.72</v>
       </c>
       <c r="C7" t="n">
-        <v>7141.91</v>
+        <v>7523.72</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6864.06</v>
+        <v>7639.49</v>
       </c>
       <c r="C8" t="n">
-        <v>6864.06</v>
+        <v>7639.49</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>107311.75</v>
+        <v>117250.09</v>
       </c>
       <c r="C9" t="n">
-        <v>107311.75</v>
+        <v>117250.09</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-09</t>
+          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-10</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26471.04</v>
+        <v>28874.22</v>
       </c>
       <c r="C3" t="n">
-        <v>26471.04</v>
+        <v>28874.22</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25857.53</v>
+        <v>27723.45</v>
       </c>
       <c r="C4" t="n">
-        <v>25857.53</v>
+        <v>27723.45</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>29461.95</v>
+        <v>32892.56</v>
       </c>
       <c r="C5" t="n">
-        <v>29461.95</v>
+        <v>32892.56</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20296.36</v>
+        <v>22139.22</v>
       </c>
       <c r="C6" t="n">
-        <v>20296.36</v>
+        <v>22139.22</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7523.72</v>
+        <v>8938.639999999999</v>
       </c>
       <c r="C7" t="n">
-        <v>7523.72</v>
+        <v>8938.639999999999</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7639.49</v>
+        <v>8471.309999999999</v>
       </c>
       <c r="C8" t="n">
-        <v>7639.49</v>
+        <v>8471.309999999999</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>117250.09</v>
+        <v>129039.4</v>
       </c>
       <c r="C9" t="n">
-        <v>117250.09</v>
+        <v>129039.4</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-10</t>
+          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-11</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>28874.22</v>
+        <v>32177.39</v>
       </c>
       <c r="C3" t="n">
-        <v>28874.22</v>
+        <v>32177.39</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>27723.45</v>
+        <v>30387.7</v>
       </c>
       <c r="C4" t="n">
-        <v>27723.45</v>
+        <v>30387.7</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32892.56</v>
+        <v>36335.61</v>
       </c>
       <c r="C5" t="n">
-        <v>32892.56</v>
+        <v>36335.61</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22139.22</v>
+        <v>24753.29</v>
       </c>
       <c r="C6" t="n">
-        <v>22139.22</v>
+        <v>24753.29</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8938.639999999999</v>
+        <v>10325.84</v>
       </c>
       <c r="C7" t="n">
-        <v>8938.639999999999</v>
+        <v>10325.84</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8471.309999999999</v>
+        <v>9548.98</v>
       </c>
       <c r="C8" t="n">
-        <v>8471.309999999999</v>
+        <v>9548.98</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>129039.4</v>
+        <v>143528.81</v>
       </c>
       <c r="C9" t="n">
-        <v>129039.4</v>
+        <v>143528.81</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-11</t>
+          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-12</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>32177.39</v>
+        <v>36590.25</v>
       </c>
       <c r="C3" t="n">
-        <v>32177.39</v>
+        <v>36590.25</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30387.7</v>
+        <v>34961.74</v>
       </c>
       <c r="C4" t="n">
-        <v>30387.7</v>
+        <v>34961.74</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>36335.61</v>
+        <v>41175.02</v>
       </c>
       <c r="C5" t="n">
-        <v>36335.61</v>
+        <v>41175.02</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24753.29</v>
+        <v>28360.4</v>
       </c>
       <c r="C6" t="n">
-        <v>24753.29</v>
+        <v>28360.4</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10325.84</v>
+        <v>11376.27</v>
       </c>
       <c r="C7" t="n">
-        <v>10325.84</v>
+        <v>11376.27</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9548.98</v>
+        <v>11089.29</v>
       </c>
       <c r="C8" t="n">
-        <v>9548.98</v>
+        <v>11089.29</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>143528.81</v>
+        <v>163552.97</v>
       </c>
       <c r="C9" t="n">
-        <v>143528.81</v>
+        <v>163552.97</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-12</t>
+          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-13</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>36590.25</v>
+        <v>40471.27</v>
       </c>
       <c r="C3" t="n">
-        <v>36590.25</v>
+        <v>40471.27</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>34961.74</v>
+        <v>38252.06</v>
       </c>
       <c r="C4" t="n">
-        <v>34961.74</v>
+        <v>38252.06</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>41175.02</v>
+        <v>45787.52</v>
       </c>
       <c r="C5" t="n">
-        <v>41175.02</v>
+        <v>45787.52</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>28360.4</v>
+        <v>30919.83</v>
       </c>
       <c r="C6" t="n">
-        <v>28360.4</v>
+        <v>30919.83</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11376.27</v>
+        <v>11862.56</v>
       </c>
       <c r="C7" t="n">
-        <v>11376.27</v>
+        <v>11862.56</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11089.29</v>
+        <v>12663.58</v>
       </c>
       <c r="C8" t="n">
-        <v>11089.29</v>
+        <v>12663.58</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>163552.97</v>
+        <v>179956.82</v>
       </c>
       <c r="C9" t="n">
-        <v>163552.97</v>
+        <v>179956.82</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-13</t>
+          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-14</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>40471.27</v>
+        <v>43031.8</v>
       </c>
       <c r="C3" t="n">
-        <v>40471.27</v>
+        <v>43031.8</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38252.06</v>
+        <v>40514.63</v>
       </c>
       <c r="C4" t="n">
-        <v>38252.06</v>
+        <v>40514.63</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>45787.52</v>
+        <v>48884.95</v>
       </c>
       <c r="C5" t="n">
-        <v>45787.52</v>
+        <v>48884.95</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30919.83</v>
+        <v>31935.21</v>
       </c>
       <c r="C6" t="n">
-        <v>30919.83</v>
+        <v>31935.21</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11862.56</v>
+        <v>12105.94</v>
       </c>
       <c r="C7" t="n">
-        <v>11862.56</v>
+        <v>12105.94</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12663.58</v>
+        <v>13512.84</v>
       </c>
       <c r="C8" t="n">
-        <v>12663.58</v>
+        <v>13512.84</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>179956.82</v>
+        <v>189985.37</v>
       </c>
       <c r="C9" t="n">
-        <v>179956.82</v>
+        <v>189985.37</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-14</t>
+          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-15</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>43031.8</v>
+        <v>46182.21</v>
       </c>
       <c r="C3" t="n">
-        <v>43031.8</v>
+        <v>46182.21</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>40514.63</v>
+        <v>42349.24</v>
       </c>
       <c r="C4" t="n">
-        <v>40514.63</v>
+        <v>42349.24</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>48884.95</v>
+        <v>52250.6</v>
       </c>
       <c r="C5" t="n">
-        <v>48884.95</v>
+        <v>52250.6</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31935.21</v>
+        <v>33948.57</v>
       </c>
       <c r="C6" t="n">
-        <v>31935.21</v>
+        <v>33948.57</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12105.94</v>
+        <v>12418.71</v>
       </c>
       <c r="C7" t="n">
-        <v>12105.94</v>
+        <v>12418.71</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13512.84</v>
+        <v>15098.2</v>
       </c>
       <c r="C8" t="n">
-        <v>13512.84</v>
+        <v>15098.2</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>189985.37</v>
+        <v>202247.53</v>
       </c>
       <c r="C9" t="n">
-        <v>189985.37</v>
+        <v>202247.53</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-15</t>
+          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-16</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>46182.21</v>
+        <v>48581.69</v>
       </c>
       <c r="C3" t="n">
-        <v>46182.21</v>
+        <v>48581.69</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>42349.24</v>
+        <v>44694.46</v>
       </c>
       <c r="C4" t="n">
-        <v>42349.24</v>
+        <v>44694.46</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>52250.6</v>
+        <v>54929.35</v>
       </c>
       <c r="C5" t="n">
-        <v>52250.6</v>
+        <v>54929.35</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>33948.57</v>
+        <v>35695.81</v>
       </c>
       <c r="C6" t="n">
-        <v>33948.57</v>
+        <v>35695.81</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15098.2</v>
+        <v>15888.8</v>
       </c>
       <c r="C8" t="n">
-        <v>15098.2</v>
+        <v>15888.8</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>202247.53</v>
+        <v>212208.82</v>
       </c>
       <c r="C9" t="n">
-        <v>202247.53</v>
+        <v>212208.82</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-16</t>
+          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-17</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>48581.69</v>
+        <v>50753.42</v>
       </c>
       <c r="C3" t="n">
-        <v>48581.69</v>
+        <v>50753.42</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44694.46</v>
+        <v>46718.69</v>
       </c>
       <c r="C4" t="n">
-        <v>44694.46</v>
+        <v>46718.69</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>54929.35</v>
+        <v>58606.49</v>
       </c>
       <c r="C5" t="n">
-        <v>54929.35</v>
+        <v>58606.49</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>35695.81</v>
+        <v>37134.63</v>
       </c>
       <c r="C6" t="n">
-        <v>35695.81</v>
+        <v>37134.63</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12418.71</v>
+        <v>12666.41</v>
       </c>
       <c r="C7" t="n">
-        <v>12418.71</v>
+        <v>12666.41</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15888.8</v>
+        <v>16961.7</v>
       </c>
       <c r="C8" t="n">
-        <v>15888.8</v>
+        <v>16961.7</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>212208.82</v>
+        <v>222841.34</v>
       </c>
       <c r="C9" t="n">
-        <v>212208.82</v>
+        <v>222841.34</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-17</t>
+          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-18</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>50753.42</v>
+        <v>54035.23</v>
       </c>
       <c r="C3" t="n">
-        <v>50753.42</v>
+        <v>54035.23</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>46718.69</v>
+        <v>49163.08</v>
       </c>
       <c r="C4" t="n">
-        <v>46718.69</v>
+        <v>49163.08</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>58606.49</v>
+        <v>62660.72</v>
       </c>
       <c r="C5" t="n">
-        <v>58606.49</v>
+        <v>62660.72</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>37134.63</v>
+        <v>40313.11</v>
       </c>
       <c r="C6" t="n">
-        <v>37134.63</v>
+        <v>40313.11</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12666.41</v>
+        <v>13338.49</v>
       </c>
       <c r="C7" t="n">
-        <v>12666.41</v>
+        <v>13338.49</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16961.7</v>
+        <v>18374.91</v>
       </c>
       <c r="C8" t="n">
-        <v>16961.7</v>
+        <v>18374.91</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>222841.34</v>
+        <v>237885.54</v>
       </c>
       <c r="C9" t="n">
-        <v>222841.34</v>
+        <v>237885.54</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-18</t>
+          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-19</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>54035.23</v>
+        <v>59306.62</v>
       </c>
       <c r="C3" t="n">
-        <v>54035.23</v>
+        <v>59306.62</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>49163.08</v>
+        <v>53578.42</v>
       </c>
       <c r="C4" t="n">
-        <v>49163.08</v>
+        <v>53578.42</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>62660.72</v>
+        <v>67714.39</v>
       </c>
       <c r="C5" t="n">
-        <v>62660.72</v>
+        <v>67714.39</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>40313.11</v>
+        <v>43861.28</v>
       </c>
       <c r="C6" t="n">
-        <v>40313.11</v>
+        <v>43861.28</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13338.49</v>
+        <v>14190.74</v>
       </c>
       <c r="C7" t="n">
-        <v>13338.49</v>
+        <v>14190.74</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18374.91</v>
+        <v>19679.78</v>
       </c>
       <c r="C8" t="n">
-        <v>18374.91</v>
+        <v>19679.78</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>237885.54</v>
+        <v>258331.23</v>
       </c>
       <c r="C9" t="n">
-        <v>237885.54</v>
+        <v>258331.23</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-19</t>
+          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-20</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>59306.62</v>
+        <v>63889.87</v>
       </c>
       <c r="C3" t="n">
-        <v>59306.62</v>
+        <v>63889.87</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>53578.42</v>
+        <v>57721.88</v>
       </c>
       <c r="C4" t="n">
-        <v>53578.42</v>
+        <v>57721.88</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>67714.39</v>
+        <v>73066.45</v>
       </c>
       <c r="C5" t="n">
-        <v>67714.39</v>
+        <v>73066.45</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>43861.28</v>
+        <v>47208.79</v>
       </c>
       <c r="C6" t="n">
-        <v>43861.28</v>
+        <v>47208.79</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14190.74</v>
+        <v>15072.47</v>
       </c>
       <c r="C7" t="n">
-        <v>14190.74</v>
+        <v>15072.47</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19679.78</v>
+        <v>20984.4</v>
       </c>
       <c r="C8" t="n">
-        <v>19679.78</v>
+        <v>20984.4</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>258331.23</v>
+        <v>277943.86</v>
       </c>
       <c r="C9" t="n">
-        <v>258331.23</v>
+        <v>277943.86</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-20</t>
+          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-21</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>63889.87</v>
+        <v>66736.28999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>63889.87</v>
+        <v>66736.28999999999</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>57721.88</v>
+        <v>59507.53</v>
       </c>
       <c r="C4" t="n">
-        <v>57721.88</v>
+        <v>59507.53</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>73066.45</v>
+        <v>76417.55</v>
       </c>
       <c r="C5" t="n">
-        <v>73066.45</v>
+        <v>76417.55</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>47208.79</v>
+        <v>48535</v>
       </c>
       <c r="C6" t="n">
-        <v>47208.79</v>
+        <v>48535</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15072.47</v>
+        <v>15512.61</v>
       </c>
       <c r="C7" t="n">
-        <v>15072.47</v>
+        <v>15512.61</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20984.4</v>
+        <v>21746.96</v>
       </c>
       <c r="C8" t="n">
-        <v>20984.4</v>
+        <v>21746.96</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>277943.86</v>
+        <v>288455.94</v>
       </c>
       <c r="C9" t="n">
-        <v>277943.86</v>
+        <v>288455.94</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-21</t>
+          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-22</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>66736.28999999999</v>
+        <v>69442.05</v>
       </c>
       <c r="C3" t="n">
-        <v>66736.28999999999</v>
+        <v>69442.05</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>59507.53</v>
+        <v>60965.14</v>
       </c>
       <c r="C4" t="n">
-        <v>59507.53</v>
+        <v>60965.14</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>76417.55</v>
+        <v>79846.95</v>
       </c>
       <c r="C5" t="n">
-        <v>76417.55</v>
+        <v>79846.95</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>48535</v>
+        <v>49593.8</v>
       </c>
       <c r="C6" t="n">
-        <v>48535</v>
+        <v>49593.8</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15512.61</v>
+        <v>15987.46</v>
       </c>
       <c r="C7" t="n">
-        <v>15512.61</v>
+        <v>15987.46</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>21746.96</v>
+        <v>22602.69</v>
       </c>
       <c r="C8" t="n">
-        <v>21746.96</v>
+        <v>22602.69</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>288455.94</v>
+        <v>298438.09</v>
       </c>
       <c r="C9" t="n">
-        <v>288455.94</v>
+        <v>298438.09</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-22</t>
+          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-23</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>69442.05</v>
+        <v>72154.50999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>69442.05</v>
+        <v>72154.50999999999</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>60965.14</v>
+        <v>62839.76</v>
       </c>
       <c r="C4" t="n">
-        <v>60965.14</v>
+        <v>62839.76</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>79846.95</v>
+        <v>84484.41</v>
       </c>
       <c r="C5" t="n">
-        <v>79846.95</v>
+        <v>84484.41</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>49593.8</v>
+        <v>51222.7</v>
       </c>
       <c r="C6" t="n">
-        <v>49593.8</v>
+        <v>51222.7</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15987.46</v>
+        <v>16189.78</v>
       </c>
       <c r="C7" t="n">
-        <v>15987.46</v>
+        <v>16189.78</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22602.69</v>
+        <v>23590.65</v>
       </c>
       <c r="C8" t="n">
-        <v>22602.69</v>
+        <v>23590.65</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>298438.09</v>
+        <v>310481.8100000001</v>
       </c>
       <c r="C9" t="n">
-        <v>298438.09</v>
+        <v>310481.8100000001</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-23</t>
+          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-24</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>72154.50999999999</v>
+        <v>74329.75</v>
       </c>
       <c r="C3" t="n">
-        <v>72154.50999999999</v>
+        <v>74329.75</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>62839.76</v>
+        <v>64835.72</v>
       </c>
       <c r="C4" t="n">
-        <v>62839.76</v>
+        <v>64835.72</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>84484.41</v>
+        <v>88501.25999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>84484.41</v>
+        <v>88501.25999999999</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>51222.7</v>
+        <v>52936.88</v>
       </c>
       <c r="C6" t="n">
-        <v>51222.7</v>
+        <v>52936.88</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16189.78</v>
+        <v>16348.57</v>
       </c>
       <c r="C7" t="n">
-        <v>16189.78</v>
+        <v>16348.57</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>23590.65</v>
+        <v>24488.15</v>
       </c>
       <c r="C8" t="n">
-        <v>23590.65</v>
+        <v>24488.15</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>310481.8100000001</v>
+        <v>321440.33</v>
       </c>
       <c r="C9" t="n">
-        <v>310481.8100000001</v>
+        <v>321440.33</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-24</t>
+          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-25</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>74329.75</v>
+        <v>77788.92999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>74329.75</v>
+        <v>77788.92999999999</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>64835.72</v>
+        <v>67993.84</v>
       </c>
       <c r="C4" t="n">
-        <v>64835.72</v>
+        <v>67993.84</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>88501.25999999999</v>
+        <v>92544.25</v>
       </c>
       <c r="C5" t="n">
-        <v>88501.25999999999</v>
+        <v>92544.25</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>52936.88</v>
+        <v>55998.67</v>
       </c>
       <c r="C6" t="n">
-        <v>52936.88</v>
+        <v>55998.67</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16348.57</v>
+        <v>17794.22</v>
       </c>
       <c r="C7" t="n">
-        <v>16348.57</v>
+        <v>17794.22</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24488.15</v>
+        <v>26346.74</v>
       </c>
       <c r="C8" t="n">
-        <v>24488.15</v>
+        <v>26346.74</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>321440.33</v>
+        <v>338466.65</v>
       </c>
       <c r="C9" t="n">
-        <v>321440.33</v>
+        <v>338466.65</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-25</t>
+          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-26</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>77788.92999999999</v>
+        <v>83655.07000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>77788.92999999999</v>
+        <v>83655.07000000001</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>67993.84</v>
+        <v>72297.95</v>
       </c>
       <c r="C4" t="n">
-        <v>67993.84</v>
+        <v>72297.95</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>92544.25</v>
+        <v>97878.12</v>
       </c>
       <c r="C5" t="n">
-        <v>92544.25</v>
+        <v>97878.12</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>55998.67</v>
+        <v>59578.76</v>
       </c>
       <c r="C6" t="n">
-        <v>55998.67</v>
+        <v>59578.76</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17794.22</v>
+        <v>19447.81</v>
       </c>
       <c r="C7" t="n">
-        <v>17794.22</v>
+        <v>19447.81</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26346.74</v>
+        <v>28028.28</v>
       </c>
       <c r="C8" t="n">
-        <v>26346.74</v>
+        <v>28028.28</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>338466.65</v>
+        <v>360885.99</v>
       </c>
       <c r="C9" t="n">
-        <v>338466.65</v>
+        <v>360885.99</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-26</t>
+          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-27</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>83655.07000000001</v>
+        <v>88186.05</v>
       </c>
       <c r="C3" t="n">
-        <v>83655.07000000001</v>
+        <v>88186.05</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>72297.95</v>
+        <v>76807.92</v>
       </c>
       <c r="C4" t="n">
-        <v>72297.95</v>
+        <v>76807.92</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>97878.12</v>
+        <v>102639.63</v>
       </c>
       <c r="C5" t="n">
-        <v>97878.12</v>
+        <v>102639.63</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>59578.76</v>
+        <v>63071.05</v>
       </c>
       <c r="C6" t="n">
-        <v>59578.76</v>
+        <v>63071.05</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19447.81</v>
+        <v>20880.9</v>
       </c>
       <c r="C7" t="n">
-        <v>19447.81</v>
+        <v>20880.9</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28028.28</v>
+        <v>29903.15</v>
       </c>
       <c r="C8" t="n">
-        <v>28028.28</v>
+        <v>29903.15</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>360885.99</v>
+        <v>381488.7</v>
       </c>
       <c r="C9" t="n">
-        <v>360885.99</v>
+        <v>381488.7</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-27</t>
+          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-28</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>88186.05</v>
+        <v>91397.59</v>
       </c>
       <c r="C3" t="n">
-        <v>88186.05</v>
+        <v>91397.59</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>76807.92</v>
+        <v>79186.50999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>76807.92</v>
+        <v>79186.50999999999</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>102639.63</v>
+        <v>107131.43</v>
       </c>
       <c r="C5" t="n">
-        <v>102639.63</v>
+        <v>107131.43</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>63071.05</v>
+        <v>64613.24</v>
       </c>
       <c r="C6" t="n">
-        <v>63071.05</v>
+        <v>64613.24</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20880.9</v>
+        <v>22070.42</v>
       </c>
       <c r="C7" t="n">
-        <v>20880.9</v>
+        <v>22070.42</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>29903.15</v>
+        <v>30939.06</v>
       </c>
       <c r="C8" t="n">
-        <v>29903.15</v>
+        <v>30939.06</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>381488.7</v>
+        <v>395338.2499999999</v>
       </c>
       <c r="C9" t="n">
-        <v>381488.7</v>
+        <v>395338.2499999999</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-28</t>
+          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-29</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>91397.59</v>
+        <v>93928.94</v>
       </c>
       <c r="C3" t="n">
-        <v>91397.59</v>
+        <v>93928.94</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>79186.50999999999</v>
+        <v>81407.27</v>
       </c>
       <c r="C4" t="n">
-        <v>79186.50999999999</v>
+        <v>81407.27</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>107131.43</v>
+        <v>110972.24</v>
       </c>
       <c r="C5" t="n">
-        <v>107131.43</v>
+        <v>110972.24</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>64613.24</v>
+        <v>66065.32000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>64613.24</v>
+        <v>66065.32000000001</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22070.42</v>
+        <v>23416.72</v>
       </c>
       <c r="C7" t="n">
-        <v>22070.42</v>
+        <v>23416.72</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>30939.06</v>
+        <v>31687.16</v>
       </c>
       <c r="C8" t="n">
-        <v>30939.06</v>
+        <v>31687.16</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>395338.2499999999</v>
+        <v>407477.65</v>
       </c>
       <c r="C9" t="n">
-        <v>395338.2499999999</v>
+        <v>407477.65</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-29</t>
+          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-30</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>93928.94</v>
+        <v>96440.53</v>
       </c>
       <c r="C3" t="n">
-        <v>93928.94</v>
+        <v>96440.53</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>81407.27</v>
+        <v>83684.28</v>
       </c>
       <c r="C4" t="n">
-        <v>81407.27</v>
+        <v>83684.28</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>110972.24</v>
+        <v>114593.83</v>
       </c>
       <c r="C5" t="n">
-        <v>110972.24</v>
+        <v>114593.83</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>66065.32000000001</v>
+        <v>68019.75999999999</v>
       </c>
       <c r="C6" t="n">
-        <v>66065.32000000001</v>
+        <v>68019.75999999999</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>23416.72</v>
+        <v>24298.13</v>
       </c>
       <c r="C7" t="n">
-        <v>23416.72</v>
+        <v>24298.13</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31687.16</v>
+        <v>32568.96</v>
       </c>
       <c r="C8" t="n">
-        <v>31687.16</v>
+        <v>32568.96</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>407477.65</v>
+        <v>419605.49</v>
       </c>
       <c r="C9" t="n">
-        <v>407477.65</v>
+        <v>419605.49</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-30</t>
+          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-31</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>96440.53</v>
+        <v>99607.12</v>
       </c>
       <c r="C3" t="n">
-        <v>96440.53</v>
+        <v>99607.12</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>83684.28</v>
+        <v>86168.38</v>
       </c>
       <c r="C4" t="n">
-        <v>83684.28</v>
+        <v>86168.38</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>114593.83</v>
+        <v>118145.88</v>
       </c>
       <c r="C5" t="n">
-        <v>114593.83</v>
+        <v>118145.88</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>68019.75999999999</v>
+        <v>71424.16</v>
       </c>
       <c r="C6" t="n">
-        <v>68019.75999999999</v>
+        <v>71424.16</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24298.13</v>
+        <v>24759.32</v>
       </c>
       <c r="C7" t="n">
-        <v>24298.13</v>
+        <v>24759.32</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>32568.96</v>
+        <v>34350.61</v>
       </c>
       <c r="C8" t="n">
-        <v>32568.96</v>
+        <v>34350.61</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>419605.49</v>
+        <v>434455.47</v>
       </c>
       <c r="C9" t="n">
-        <v>419605.49</v>
+        <v>434455.47</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-31</t>
+          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-01</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>99607.12</v>
+        <v>3195.6</v>
       </c>
       <c r="C3" t="n">
-        <v>99607.12</v>
+        <v>3195.6</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>86168.38</v>
+        <v>2505.44</v>
       </c>
       <c r="C4" t="n">
-        <v>86168.38</v>
+        <v>2505.44</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>118145.88</v>
+        <v>3958.83</v>
       </c>
       <c r="C5" t="n">
-        <v>118145.88</v>
+        <v>3958.83</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>71424.16</v>
+        <v>2723.4</v>
       </c>
       <c r="C6" t="n">
-        <v>71424.16</v>
+        <v>2723.4</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24759.32</v>
+        <v>458.78</v>
       </c>
       <c r="C7" t="n">
-        <v>24759.32</v>
+        <v>458.78</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>34350.61</v>
+        <v>1520.49</v>
       </c>
       <c r="C8" t="n">
-        <v>34350.61</v>
+        <v>1520.49</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>434455.47</v>
+        <v>14362.54</v>
       </c>
       <c r="C9" t="n">
-        <v>434455.47</v>
+        <v>14362.54</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-01</t>
+          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-02</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3195.6</v>
+        <v>8511.02</v>
       </c>
       <c r="C3" t="n">
-        <v>3195.6</v>
+        <v>8511.02</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2505.44</v>
+        <v>7105.8</v>
       </c>
       <c r="C4" t="n">
-        <v>2505.44</v>
+        <v>7105.8</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3958.83</v>
+        <v>9634.440000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>3958.83</v>
+        <v>9634.440000000001</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2723.4</v>
+        <v>6435.61</v>
       </c>
       <c r="C6" t="n">
-        <v>2723.4</v>
+        <v>6435.61</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>458.78</v>
+        <v>1849.92</v>
       </c>
       <c r="C7" t="n">
-        <v>458.78</v>
+        <v>1849.92</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1520.49</v>
+        <v>3043.24</v>
       </c>
       <c r="C8" t="n">
-        <v>1520.49</v>
+        <v>3043.24</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14362.54</v>
+        <v>36580.03</v>
       </c>
       <c r="C9" t="n">
-        <v>14362.54</v>
+        <v>36580.03</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-02</t>
+          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-03</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8511.02</v>
+        <v>12610.34</v>
       </c>
       <c r="C3" t="n">
-        <v>8511.02</v>
+        <v>12610.34</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7105.8</v>
+        <v>10524.72</v>
       </c>
       <c r="C4" t="n">
-        <v>7105.8</v>
+        <v>10524.72</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9634.440000000001</v>
+        <v>14955.71</v>
       </c>
       <c r="C5" t="n">
-        <v>9634.440000000001</v>
+        <v>14955.71</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6435.61</v>
+        <v>9873.98</v>
       </c>
       <c r="C6" t="n">
-        <v>6435.61</v>
+        <v>9873.98</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1849.92</v>
+        <v>2943.19</v>
       </c>
       <c r="C7" t="n">
-        <v>1849.92</v>
+        <v>2943.19</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3043.24</v>
+        <v>4913.64</v>
       </c>
       <c r="C8" t="n">
-        <v>3043.24</v>
+        <v>4913.64</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>36580.03</v>
+        <v>55821.58</v>
       </c>
       <c r="C9" t="n">
-        <v>36580.03</v>
+        <v>55821.58</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-03</t>
+          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-04</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12610.34</v>
+        <v>15510.37</v>
       </c>
       <c r="C3" t="n">
-        <v>12610.34</v>
+        <v>15510.37</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10524.72</v>
+        <v>12874.47</v>
       </c>
       <c r="C4" t="n">
-        <v>10524.72</v>
+        <v>12874.47</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14955.71</v>
+        <v>18688.44</v>
       </c>
       <c r="C5" t="n">
-        <v>14955.71</v>
+        <v>18688.44</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9873.98</v>
+        <v>11347.48</v>
       </c>
       <c r="C6" t="n">
-        <v>9873.98</v>
+        <v>11347.48</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2943.19</v>
+        <v>3793.94</v>
       </c>
       <c r="C7" t="n">
-        <v>2943.19</v>
+        <v>3793.94</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4913.64</v>
+        <v>5753.96</v>
       </c>
       <c r="C8" t="n">
-        <v>4913.64</v>
+        <v>5753.96</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>55821.58</v>
+        <v>67968.66</v>
       </c>
       <c r="C9" t="n">
-        <v>55821.58</v>
+        <v>67968.66</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-04</t>
+          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-05</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15510.37</v>
+        <v>18074.45</v>
       </c>
       <c r="C3" t="n">
-        <v>15510.37</v>
+        <v>18074.45</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12874.47</v>
+        <v>14500.25</v>
       </c>
       <c r="C4" t="n">
-        <v>12874.47</v>
+        <v>14500.25</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18688.44</v>
+        <v>21817.54</v>
       </c>
       <c r="C5" t="n">
-        <v>18688.44</v>
+        <v>21817.54</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11347.48</v>
+        <v>13095.42</v>
       </c>
       <c r="C6" t="n">
-        <v>11347.48</v>
+        <v>13095.42</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3793.94</v>
+        <v>4916.72</v>
       </c>
       <c r="C7" t="n">
-        <v>3793.94</v>
+        <v>4916.72</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5753.96</v>
+        <v>6530.13</v>
       </c>
       <c r="C8" t="n">
-        <v>5753.96</v>
+        <v>6530.13</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>67968.66</v>
+        <v>78934.51000000001</v>
       </c>
       <c r="C9" t="n">
-        <v>67968.66</v>
+        <v>78934.51000000001</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-05</t>
+          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-06</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18074.45</v>
+        <v>21045.56</v>
       </c>
       <c r="C3" t="n">
-        <v>18074.45</v>
+        <v>21045.56</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14500.25</v>
+        <v>15963.79</v>
       </c>
       <c r="C4" t="n">
-        <v>14500.25</v>
+        <v>15963.79</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21817.54</v>
+        <v>25527.98</v>
       </c>
       <c r="C5" t="n">
-        <v>21817.54</v>
+        <v>25527.98</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13095.42</v>
+        <v>14706.71</v>
       </c>
       <c r="C6" t="n">
-        <v>13095.42</v>
+        <v>14706.71</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4916.72</v>
+        <v>5398.07</v>
       </c>
       <c r="C7" t="n">
-        <v>4916.72</v>
+        <v>5398.07</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6530.13</v>
+        <v>7594.25</v>
       </c>
       <c r="C8" t="n">
-        <v>6530.13</v>
+        <v>7594.25</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>78934.51000000001</v>
+        <v>90236.36000000002</v>
       </c>
       <c r="C9" t="n">
-        <v>78934.51000000001</v>
+        <v>90236.36000000002</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-06</t>
+          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-07</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21045.56</v>
+        <v>23750.72</v>
       </c>
       <c r="C3" t="n">
-        <v>21045.56</v>
+        <v>23750.72</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15963.79</v>
+        <v>17679.34</v>
       </c>
       <c r="C4" t="n">
-        <v>15963.79</v>
+        <v>17679.34</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25527.98</v>
+        <v>29085.97</v>
       </c>
       <c r="C5" t="n">
-        <v>25527.98</v>
+        <v>29085.97</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14706.71</v>
+        <v>16163.88</v>
       </c>
       <c r="C6" t="n">
-        <v>14706.71</v>
+        <v>16163.88</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5398.07</v>
+        <v>5608.57</v>
       </c>
       <c r="C7" t="n">
-        <v>5398.07</v>
+        <v>5608.57</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7594.25</v>
+        <v>8271.370000000001</v>
       </c>
       <c r="C8" t="n">
-        <v>7594.25</v>
+        <v>8271.370000000001</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>90236.36000000002</v>
+        <v>100559.85</v>
       </c>
       <c r="C9" t="n">
-        <v>90236.36000000002</v>
+        <v>100559.85</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-07</t>
+          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-08</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23750.72</v>
+        <v>27446.86</v>
       </c>
       <c r="C3" t="n">
-        <v>23750.72</v>
+        <v>27446.86</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17679.34</v>
+        <v>20045.27</v>
       </c>
       <c r="C4" t="n">
-        <v>17679.34</v>
+        <v>20045.27</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>29085.97</v>
+        <v>32581.45</v>
       </c>
       <c r="C5" t="n">
-        <v>29085.97</v>
+        <v>32581.45</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16163.88</v>
+        <v>19416.97</v>
       </c>
       <c r="C6" t="n">
-        <v>16163.88</v>
+        <v>19416.97</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5608.57</v>
+        <v>5905.68</v>
       </c>
       <c r="C7" t="n">
-        <v>5608.57</v>
+        <v>5905.68</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8271.370000000001</v>
+        <v>9716.780000000001</v>
       </c>
       <c r="C8" t="n">
-        <v>8271.370000000001</v>
+        <v>9716.780000000001</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>100559.85</v>
+        <v>115113.01</v>
       </c>
       <c r="C9" t="n">
-        <v>100559.85</v>
+        <v>115113.01</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-08</t>
+          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-09</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>27446.86</v>
+        <v>33420.18</v>
       </c>
       <c r="C3" t="n">
-        <v>27446.86</v>
+        <v>33420.18</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20045.27</v>
+        <v>24065.19</v>
       </c>
       <c r="C4" t="n">
-        <v>20045.27</v>
+        <v>24065.19</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32581.45</v>
+        <v>38518.61</v>
       </c>
       <c r="C5" t="n">
-        <v>32581.45</v>
+        <v>38518.61</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19416.97</v>
+        <v>23502.98</v>
       </c>
       <c r="C6" t="n">
-        <v>19416.97</v>
+        <v>23502.98</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5905.68</v>
+        <v>7069.92</v>
       </c>
       <c r="C7" t="n">
-        <v>5905.68</v>
+        <v>7069.92</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9716.780000000001</v>
+        <v>11269.05</v>
       </c>
       <c r="C8" t="n">
-        <v>9716.780000000001</v>
+        <v>11269.05</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>115113.01</v>
+        <v>137845.93</v>
       </c>
       <c r="C9" t="n">
-        <v>115113.01</v>
+        <v>137845.93</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-09</t>
+          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-10</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33420.18</v>
+        <v>37587.28</v>
       </c>
       <c r="C3" t="n">
-        <v>33420.18</v>
+        <v>37587.28</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24065.19</v>
+        <v>27011.93</v>
       </c>
       <c r="C4" t="n">
-        <v>24065.19</v>
+        <v>27011.93</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>38518.61</v>
+        <v>43271.76</v>
       </c>
       <c r="C5" t="n">
-        <v>38518.61</v>
+        <v>43271.76</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23502.98</v>
+        <v>27020.86</v>
       </c>
       <c r="C6" t="n">
-        <v>23502.98</v>
+        <v>27020.86</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7069.92</v>
+        <v>7839.33</v>
       </c>
       <c r="C7" t="n">
-        <v>7069.92</v>
+        <v>7839.33</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11269.05</v>
+        <v>12529.05</v>
       </c>
       <c r="C8" t="n">
-        <v>11269.05</v>
+        <v>12529.05</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>137845.93</v>
+        <v>155260.21</v>
       </c>
       <c r="C9" t="n">
-        <v>137845.93</v>
+        <v>155260.21</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-10</t>
+          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-11</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>37587.28</v>
+        <v>39396.53</v>
       </c>
       <c r="C3" t="n">
-        <v>37587.28</v>
+        <v>39396.53</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>27011.93</v>
+        <v>29183.6</v>
       </c>
       <c r="C4" t="n">
-        <v>27011.93</v>
+        <v>29183.6</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>43271.76</v>
+        <v>46320.27</v>
       </c>
       <c r="C5" t="n">
-        <v>43271.76</v>
+        <v>46320.27</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>27020.86</v>
+        <v>28709.03</v>
       </c>
       <c r="C6" t="n">
-        <v>27020.86</v>
+        <v>28709.03</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7839.33</v>
+        <v>8386.16</v>
       </c>
       <c r="C7" t="n">
-        <v>7839.33</v>
+        <v>8386.16</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12529.05</v>
+        <v>13056.95</v>
       </c>
       <c r="C8" t="n">
-        <v>12529.05</v>
+        <v>13056.95</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>155260.21</v>
+        <v>165052.54</v>
       </c>
       <c r="C9" t="n">
-        <v>155260.21</v>
+        <v>165052.54</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-11</t>
+          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-12</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>39396.53</v>
+        <v>41648.69</v>
       </c>
       <c r="C3" t="n">
-        <v>39396.53</v>
+        <v>41648.69</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29183.6</v>
+        <v>31199.41</v>
       </c>
       <c r="C4" t="n">
-        <v>29183.6</v>
+        <v>31199.41</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>46320.27</v>
+        <v>49027.66</v>
       </c>
       <c r="C5" t="n">
-        <v>46320.27</v>
+        <v>49027.66</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>28709.03</v>
+        <v>30339.08</v>
       </c>
       <c r="C6" t="n">
-        <v>28709.03</v>
+        <v>30339.08</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8386.16</v>
+        <v>9146.75</v>
       </c>
       <c r="C7" t="n">
-        <v>8386.16</v>
+        <v>9146.75</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13056.95</v>
+        <v>13634.22</v>
       </c>
       <c r="C8" t="n">
-        <v>13056.95</v>
+        <v>13634.22</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>165052.54</v>
+        <v>174995.81</v>
       </c>
       <c r="C9" t="n">
-        <v>165052.54</v>
+        <v>174995.81</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-12</t>
+          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-13</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>41648.69</v>
+        <v>43519.86</v>
       </c>
       <c r="C3" t="n">
-        <v>41648.69</v>
+        <v>43519.86</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>31199.41</v>
+        <v>33217.12</v>
       </c>
       <c r="C4" t="n">
-        <v>31199.41</v>
+        <v>33217.12</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>49027.66</v>
+        <v>51831.36</v>
       </c>
       <c r="C5" t="n">
-        <v>49027.66</v>
+        <v>51831.36</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30339.08</v>
+        <v>31439.08</v>
       </c>
       <c r="C6" t="n">
-        <v>30339.08</v>
+        <v>31439.08</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9146.75</v>
+        <v>9893.309999999999</v>
       </c>
       <c r="C7" t="n">
-        <v>9146.75</v>
+        <v>9893.309999999999</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13634.22</v>
+        <v>14417.57</v>
       </c>
       <c r="C8" t="n">
-        <v>13634.22</v>
+        <v>14417.57</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>174995.81</v>
+        <v>184318.3</v>
       </c>
       <c r="C9" t="n">
-        <v>174995.81</v>
+        <v>184318.3</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-13</t>
+          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-14</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>43519.86</v>
+        <v>45321.86</v>
       </c>
       <c r="C3" t="n">
-        <v>43519.86</v>
+        <v>45321.86</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>33217.12</v>
+        <v>35616.76</v>
       </c>
       <c r="C4" t="n">
-        <v>33217.12</v>
+        <v>35616.76</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>51831.36</v>
+        <v>54700.8</v>
       </c>
       <c r="C5" t="n">
-        <v>51831.36</v>
+        <v>54700.8</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31439.08</v>
+        <v>33000.1</v>
       </c>
       <c r="C6" t="n">
-        <v>31439.08</v>
+        <v>33000.1</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9893.309999999999</v>
+        <v>10621.88</v>
       </c>
       <c r="C7" t="n">
-        <v>9893.309999999999</v>
+        <v>10621.88</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14417.57</v>
+        <v>15187.51</v>
       </c>
       <c r="C8" t="n">
-        <v>14417.57</v>
+        <v>15187.51</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>184318.3</v>
+        <v>194448.91</v>
       </c>
       <c r="C9" t="n">
-        <v>184318.3</v>
+        <v>194448.91</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-14</t>
+          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-15</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45321.86</v>
+        <v>48050.22</v>
       </c>
       <c r="C3" t="n">
-        <v>45321.86</v>
+        <v>48050.22</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>35616.76</v>
+        <v>37777.38</v>
       </c>
       <c r="C4" t="n">
-        <v>35616.76</v>
+        <v>37777.38</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>54700.8</v>
+        <v>57705</v>
       </c>
       <c r="C5" t="n">
-        <v>54700.8</v>
+        <v>57705</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>33000.1</v>
+        <v>37816.94</v>
       </c>
       <c r="C6" t="n">
-        <v>33000.1</v>
+        <v>37816.94</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10621.88</v>
+        <v>11449.19</v>
       </c>
       <c r="C7" t="n">
-        <v>10621.88</v>
+        <v>11449.19</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15187.51</v>
+        <v>16974.4</v>
       </c>
       <c r="C8" t="n">
-        <v>15187.51</v>
+        <v>16974.4</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>194448.91</v>
+        <v>209773.13</v>
       </c>
       <c r="C9" t="n">
-        <v>194448.91</v>
+        <v>209773.13</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-15</t>
+          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-16</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>48050.22</v>
+        <v>53092.65</v>
       </c>
       <c r="C3" t="n">
-        <v>48050.22</v>
+        <v>53092.65</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>37777.38</v>
+        <v>42680.8</v>
       </c>
       <c r="C4" t="n">
-        <v>37777.38</v>
+        <v>42680.8</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>57705</v>
+        <v>63069.32</v>
       </c>
       <c r="C5" t="n">
-        <v>57705</v>
+        <v>63069.32</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>37816.94</v>
+        <v>41642.22</v>
       </c>
       <c r="C6" t="n">
-        <v>37816.94</v>
+        <v>41642.22</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11449.19</v>
+        <v>12407.28</v>
       </c>
       <c r="C7" t="n">
-        <v>11449.19</v>
+        <v>12407.28</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16974.4</v>
+        <v>18668.25</v>
       </c>
       <c r="C8" t="n">
-        <v>16974.4</v>
+        <v>18668.25</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>209773.13</v>
+        <v>231560.52</v>
       </c>
       <c r="C9" t="n">
-        <v>209773.13</v>
+        <v>231560.52</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-16</t>
+          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-17</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>53092.65</v>
+        <v>57261.63</v>
       </c>
       <c r="C3" t="n">
-        <v>53092.65</v>
+        <v>57261.63</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>42680.8</v>
+        <v>46736.14</v>
       </c>
       <c r="C4" t="n">
-        <v>42680.8</v>
+        <v>46736.14</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>63069.32</v>
+        <v>67796.00999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>63069.32</v>
+        <v>67796.00999999999</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>41642.22</v>
+        <v>44471.62</v>
       </c>
       <c r="C6" t="n">
-        <v>41642.22</v>
+        <v>44471.62</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12407.28</v>
+        <v>13214.59</v>
       </c>
       <c r="C7" t="n">
-        <v>12407.28</v>
+        <v>13214.59</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18668.25</v>
+        <v>20375.41</v>
       </c>
       <c r="C8" t="n">
-        <v>18668.25</v>
+        <v>20375.41</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>231560.52</v>
+        <v>249855.4</v>
       </c>
       <c r="C9" t="n">
-        <v>231560.52</v>
+        <v>249855.4</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-17</t>
+          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-18</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>57261.63</v>
+        <v>59029.99</v>
       </c>
       <c r="C3" t="n">
-        <v>57261.63</v>
+        <v>59029.99</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>46736.14</v>
+        <v>48639.56</v>
       </c>
       <c r="C4" t="n">
-        <v>46736.14</v>
+        <v>48639.56</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>67796.00999999999</v>
+        <v>70343</v>
       </c>
       <c r="C5" t="n">
-        <v>67796.00999999999</v>
+        <v>70343</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>44471.62</v>
+        <v>45434.17</v>
       </c>
       <c r="C6" t="n">
-        <v>44471.62</v>
+        <v>45434.17</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13214.59</v>
+        <v>13759.43</v>
       </c>
       <c r="C7" t="n">
-        <v>13214.59</v>
+        <v>13759.43</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20375.41</v>
+        <v>21060.78</v>
       </c>
       <c r="C8" t="n">
-        <v>20375.41</v>
+        <v>21060.78</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>249855.4</v>
+        <v>258266.93</v>
       </c>
       <c r="C9" t="n">
-        <v>249855.4</v>
+        <v>258266.93</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-18</t>
+          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-19</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>59029.99</v>
+        <v>60802.34</v>
       </c>
       <c r="C3" t="n">
-        <v>59029.99</v>
+        <v>60802.34</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>48639.56</v>
+        <v>51015.99</v>
       </c>
       <c r="C4" t="n">
-        <v>48639.56</v>
+        <v>51015.99</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>70343</v>
+        <v>73032.38</v>
       </c>
       <c r="C5" t="n">
-        <v>70343</v>
+        <v>73032.38</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>45434.17</v>
+        <v>46368.31</v>
       </c>
       <c r="C6" t="n">
-        <v>45434.17</v>
+        <v>46368.31</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13759.43</v>
+        <v>14405.2</v>
       </c>
       <c r="C7" t="n">
-        <v>13759.43</v>
+        <v>14405.2</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>21060.78</v>
+        <v>21840.99</v>
       </c>
       <c r="C8" t="n">
-        <v>21060.78</v>
+        <v>21840.99</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>258266.93</v>
+        <v>267465.21</v>
       </c>
       <c r="C9" t="n">
-        <v>258266.93</v>
+        <v>267465.21</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-19</t>
+          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-20</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>60802.34</v>
+        <v>62353.6</v>
       </c>
       <c r="C3" t="n">
-        <v>60802.34</v>
+        <v>62353.6</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>51015.99</v>
+        <v>53488.7</v>
       </c>
       <c r="C4" t="n">
-        <v>51015.99</v>
+        <v>53488.7</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>73032.38</v>
+        <v>75656.36</v>
       </c>
       <c r="C5" t="n">
-        <v>73032.38</v>
+        <v>75656.36</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>46368.31</v>
+        <v>47342.45</v>
       </c>
       <c r="C6" t="n">
-        <v>46368.31</v>
+        <v>47342.45</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14405.2</v>
+        <v>15013.84</v>
       </c>
       <c r="C7" t="n">
-        <v>14405.2</v>
+        <v>15013.84</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>21840.99</v>
+        <v>22612.36</v>
       </c>
       <c r="C8" t="n">
-        <v>21840.99</v>
+        <v>22612.36</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>267465.21</v>
+        <v>276467.31</v>
       </c>
       <c r="C9" t="n">
-        <v>267465.21</v>
+        <v>276467.31</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-20</t>
+          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-21</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>62353.6</v>
+        <v>64379.1</v>
       </c>
       <c r="C3" t="n">
-        <v>62353.6</v>
+        <v>64379.1</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>53488.7</v>
+        <v>56089.17</v>
       </c>
       <c r="C4" t="n">
-        <v>53488.7</v>
+        <v>56089.17</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>75656.36</v>
+        <v>78410.10000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>75656.36</v>
+        <v>78410.10000000001</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>47342.45</v>
+        <v>48486.76</v>
       </c>
       <c r="C6" t="n">
-        <v>47342.45</v>
+        <v>48486.76</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15013.84</v>
+        <v>15546.94</v>
       </c>
       <c r="C7" t="n">
-        <v>15013.84</v>
+        <v>15546.94</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22612.36</v>
+        <v>23240.88</v>
       </c>
       <c r="C8" t="n">
-        <v>22612.36</v>
+        <v>23240.88</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>276467.31</v>
+        <v>286152.95</v>
       </c>
       <c r="C9" t="n">
-        <v>276467.31</v>
+        <v>286152.95</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-21</t>
+          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-22</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>64379.1</v>
+        <v>66991.99000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>64379.1</v>
+        <v>66991.99000000001</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>56089.17</v>
+        <v>58447.35</v>
       </c>
       <c r="C4" t="n">
-        <v>56089.17</v>
+        <v>58447.35</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>78410.10000000001</v>
+        <v>81091.41</v>
       </c>
       <c r="C5" t="n">
-        <v>78410.10000000001</v>
+        <v>81091.41</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>48486.76</v>
+        <v>50693.05</v>
       </c>
       <c r="C6" t="n">
-        <v>48486.76</v>
+        <v>50693.05</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15546.94</v>
+        <v>16048.83</v>
       </c>
       <c r="C7" t="n">
-        <v>15546.94</v>
+        <v>16048.83</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>23240.88</v>
+        <v>24224.59</v>
       </c>
       <c r="C8" t="n">
-        <v>23240.88</v>
+        <v>24224.59</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>286152.95</v>
+        <v>297497.22</v>
       </c>
       <c r="C9" t="n">
-        <v>286152.95</v>
+        <v>297497.22</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-22</t>
+          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-23</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>66991.99000000001</v>
+        <v>71849.71000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>66991.99000000001</v>
+        <v>71849.71000000001</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>58447.35</v>
+        <v>61901.25</v>
       </c>
       <c r="C4" t="n">
-        <v>58447.35</v>
+        <v>61901.25</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>81091.41</v>
+        <v>85668.53999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>81091.41</v>
+        <v>85668.53999999999</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>50693.05</v>
+        <v>53619.96</v>
       </c>
       <c r="C6" t="n">
-        <v>50693.05</v>
+        <v>53619.96</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16048.83</v>
+        <v>16825.16</v>
       </c>
       <c r="C7" t="n">
-        <v>16048.83</v>
+        <v>16825.16</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24224.59</v>
+        <v>25373.01</v>
       </c>
       <c r="C8" t="n">
-        <v>24224.59</v>
+        <v>25373.01</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>297497.22</v>
+        <v>315237.63</v>
       </c>
       <c r="C9" t="n">
-        <v>297497.22</v>
+        <v>315237.63</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-23</t>
+          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-24</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>71849.71000000001</v>
+        <v>75367</v>
       </c>
       <c r="C3" t="n">
-        <v>71849.71000000001</v>
+        <v>75367</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>61901.25</v>
+        <v>64993.46</v>
       </c>
       <c r="C4" t="n">
-        <v>61901.25</v>
+        <v>64993.46</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>85668.53999999999</v>
+        <v>90408.84</v>
       </c>
       <c r="C5" t="n">
-        <v>85668.53999999999</v>
+        <v>90408.84</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>53619.96</v>
+        <v>55840.31</v>
       </c>
       <c r="C6" t="n">
-        <v>53619.96</v>
+        <v>55840.31</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16825.16</v>
+        <v>17463.97</v>
       </c>
       <c r="C7" t="n">
-        <v>16825.16</v>
+        <v>17463.97</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>25373.01</v>
+        <v>26749.64</v>
       </c>
       <c r="C8" t="n">
-        <v>25373.01</v>
+        <v>26749.64</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>315237.63</v>
+        <v>330823.22</v>
       </c>
       <c r="C9" t="n">
-        <v>315237.63</v>
+        <v>330823.22</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-24</t>
+          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-25</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>75367</v>
+        <v>77089.25</v>
       </c>
       <c r="C3" t="n">
-        <v>75367</v>
+        <v>77089.25</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>64993.46</v>
+        <v>66889.78</v>
       </c>
       <c r="C4" t="n">
-        <v>64993.46</v>
+        <v>66889.78</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>90408.84</v>
+        <v>93026.49000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>90408.84</v>
+        <v>93026.49000000001</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>55840.31</v>
+        <v>56979.09</v>
       </c>
       <c r="C6" t="n">
-        <v>55840.31</v>
+        <v>56979.09</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17463.97</v>
+        <v>17924.71</v>
       </c>
       <c r="C7" t="n">
-        <v>17463.97</v>
+        <v>17924.71</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26749.64</v>
+        <v>27129.49</v>
       </c>
       <c r="C8" t="n">
-        <v>26749.64</v>
+        <v>27129.49</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>330823.22</v>
+        <v>339038.81</v>
       </c>
       <c r="C9" t="n">
-        <v>330823.22</v>
+        <v>339038.81</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-25</t>
+          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-26</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>77089.25</v>
+        <v>78517.3</v>
       </c>
       <c r="C3" t="n">
-        <v>77089.25</v>
+        <v>78517.3</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>66889.78</v>
+        <v>68574.28999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>66889.78</v>
+        <v>68574.28999999999</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>93026.49000000001</v>
+        <v>95528.99000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>93026.49000000001</v>
+        <v>95528.99000000001</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>56979.09</v>
+        <v>57853.94</v>
       </c>
       <c r="C6" t="n">
-        <v>56979.09</v>
+        <v>57853.94</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17924.71</v>
+        <v>18465.55</v>
       </c>
       <c r="C7" t="n">
-        <v>17924.71</v>
+        <v>18465.55</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27129.49</v>
+        <v>27587.17</v>
       </c>
       <c r="C8" t="n">
-        <v>27129.49</v>
+        <v>27587.17</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>339038.81</v>
+        <v>346527.24</v>
       </c>
       <c r="C9" t="n">
-        <v>339038.81</v>
+        <v>346527.24</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-26</t>
+          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-27</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>78517.3</v>
+        <v>79943.52</v>
       </c>
       <c r="C3" t="n">
-        <v>78517.3</v>
+        <v>79943.52</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>68574.28999999999</v>
+        <v>70031.8</v>
       </c>
       <c r="C4" t="n">
-        <v>68574.28999999999</v>
+        <v>70031.8</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>95528.99000000001</v>
+        <v>97462.81</v>
       </c>
       <c r="C5" t="n">
-        <v>95528.99000000001</v>
+        <v>97462.81</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>57853.94</v>
+        <v>59194.38</v>
       </c>
       <c r="C6" t="n">
-        <v>57853.94</v>
+        <v>59194.38</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18465.55</v>
+        <v>19199.17</v>
       </c>
       <c r="C7" t="n">
-        <v>18465.55</v>
+        <v>19199.17</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27587.17</v>
+        <v>28316.32</v>
       </c>
       <c r="C8" t="n">
-        <v>27587.17</v>
+        <v>28316.32</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>346527.24</v>
+        <v>354148</v>
       </c>
       <c r="C9" t="n">
-        <v>346527.24</v>
+        <v>354148</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-27</t>
+          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-28</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>79943.52</v>
+        <v>81698.17</v>
       </c>
       <c r="C3" t="n">
-        <v>79943.52</v>
+        <v>81698.17</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>70031.8</v>
+        <v>72398.3</v>
       </c>
       <c r="C4" t="n">
-        <v>70031.8</v>
+        <v>72398.3</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>97462.81</v>
+        <v>99559.17999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>97462.81</v>
+        <v>99559.17999999999</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>59194.38</v>
+        <v>60295.45</v>
       </c>
       <c r="C6" t="n">
-        <v>59194.38</v>
+        <v>60295.45</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19199.17</v>
+        <v>19669.87</v>
       </c>
       <c r="C7" t="n">
-        <v>19199.17</v>
+        <v>19669.87</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28316.32</v>
+        <v>28963.76</v>
       </c>
       <c r="C8" t="n">
-        <v>28316.32</v>
+        <v>28963.76</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>354148</v>
+        <v>362584.73</v>
       </c>
       <c r="C9" t="n">
-        <v>354148</v>
+        <v>362584.73</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-28</t>
+          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-29</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>81698.17</v>
+        <v>83960.56</v>
       </c>
       <c r="C3" t="n">
-        <v>81698.17</v>
+        <v>83960.56</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>72398.3</v>
+        <v>75011.42999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>72398.3</v>
+        <v>75011.42999999999</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>99559.17999999999</v>
+        <v>102330.47</v>
       </c>
       <c r="C5" t="n">
-        <v>99559.17999999999</v>
+        <v>102330.47</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>60295.45</v>
+        <v>61866.94</v>
       </c>
       <c r="C6" t="n">
-        <v>60295.45</v>
+        <v>61866.94</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19669.87</v>
+        <v>20665.41</v>
       </c>
       <c r="C7" t="n">
-        <v>19669.87</v>
+        <v>20665.41</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28963.76</v>
+        <v>30026.19</v>
       </c>
       <c r="C8" t="n">
-        <v>28963.76</v>
+        <v>30026.19</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>362584.73</v>
+        <v>373861</v>
       </c>
       <c r="C9" t="n">
-        <v>362584.73</v>
+        <v>373861</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-29</t>
+          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-30</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>83960.56</v>
+        <v>88270.08</v>
       </c>
       <c r="C3" t="n">
-        <v>83960.56</v>
+        <v>88270.08</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>75011.42999999999</v>
+        <v>79527.33</v>
       </c>
       <c r="C4" t="n">
-        <v>75011.42999999999</v>
+        <v>79527.33</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>102330.47</v>
+        <v>107381.05</v>
       </c>
       <c r="C5" t="n">
-        <v>102330.47</v>
+        <v>107381.05</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>61866.94</v>
+        <v>65236.44</v>
       </c>
       <c r="C6" t="n">
-        <v>61866.94</v>
+        <v>65236.44</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20665.41</v>
+        <v>21710.62</v>
       </c>
       <c r="C7" t="n">
-        <v>20665.41</v>
+        <v>21710.62</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>30026.19</v>
+        <v>30946.33</v>
       </c>
       <c r="C8" t="n">
-        <v>30026.19</v>
+        <v>30946.33</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>373861</v>
+        <v>393071.85</v>
       </c>
       <c r="C9" t="n">
-        <v>373861</v>
+        <v>393071.85</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-30</t>
+          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-31</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>88270.08</v>
+        <v>92705.44</v>
       </c>
       <c r="C3" t="n">
-        <v>88270.08</v>
+        <v>92705.44</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>79527.33</v>
+        <v>83610.77</v>
       </c>
       <c r="C4" t="n">
-        <v>79527.33</v>
+        <v>83610.77</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>107381.05</v>
+        <v>112089.51</v>
       </c>
       <c r="C5" t="n">
-        <v>107381.05</v>
+        <v>112089.51</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>65236.44</v>
+        <v>69692.69</v>
       </c>
       <c r="C6" t="n">
-        <v>65236.44</v>
+        <v>69692.69</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21710.62</v>
+        <v>22598.06</v>
       </c>
       <c r="C7" t="n">
-        <v>21710.62</v>
+        <v>22598.06</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>30946.33</v>
+        <v>33096.66</v>
       </c>
       <c r="C8" t="n">
-        <v>30946.33</v>
+        <v>33096.66</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>393071.85</v>
+        <v>413793.13</v>
       </c>
       <c r="C9" t="n">
-        <v>393071.85</v>
+        <v>413793.13</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-31</t>
+          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-01</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>92705.44</v>
+        <v>3558.6</v>
       </c>
       <c r="C3" t="n">
-        <v>92705.44</v>
+        <v>3558.6</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>83610.77</v>
+        <v>3306.11</v>
       </c>
       <c r="C4" t="n">
-        <v>83610.77</v>
+        <v>3306.11</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>112089.51</v>
+        <v>4803.45</v>
       </c>
       <c r="C5" t="n">
-        <v>112089.51</v>
+        <v>4803.45</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>69692.69</v>
+        <v>3095.52</v>
       </c>
       <c r="C6" t="n">
-        <v>69692.69</v>
+        <v>3095.52</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22598.06</v>
+        <v>876.92</v>
       </c>
       <c r="C7" t="n">
-        <v>22598.06</v>
+        <v>876.92</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>33096.66</v>
+        <v>1260.88</v>
       </c>
       <c r="C8" t="n">
-        <v>33096.66</v>
+        <v>1260.88</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>413793.13</v>
+        <v>16901.48</v>
       </c>
       <c r="C9" t="n">
-        <v>413793.13</v>
+        <v>16901.48</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-01</t>
+          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-02</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3558.6</v>
+        <v>4765.19</v>
       </c>
       <c r="C3" t="n">
-        <v>3558.6</v>
+        <v>4765.19</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3306.11</v>
+        <v>4769.64</v>
       </c>
       <c r="C4" t="n">
-        <v>3306.11</v>
+        <v>4769.64</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4803.45</v>
+        <v>6145.87</v>
       </c>
       <c r="C5" t="n">
-        <v>4803.45</v>
+        <v>6145.87</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3095.52</v>
+        <v>4040.33</v>
       </c>
       <c r="C6" t="n">
-        <v>3095.52</v>
+        <v>4040.33</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>876.92</v>
+        <v>1551.77</v>
       </c>
       <c r="C7" t="n">
-        <v>876.92</v>
+        <v>1551.77</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1260.88</v>
+        <v>1519.54</v>
       </c>
       <c r="C8" t="n">
-        <v>1260.88</v>
+        <v>1519.54</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16901.48</v>
+        <v>22792.34</v>
       </c>
       <c r="C9" t="n">
-        <v>16901.48</v>
+        <v>22792.34</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-02</t>
+          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-03</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4765.19</v>
+        <v>5989.57</v>
       </c>
       <c r="C3" t="n">
-        <v>4765.19</v>
+        <v>5989.57</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4769.64</v>
+        <v>5624.98</v>
       </c>
       <c r="C4" t="n">
-        <v>4769.64</v>
+        <v>5624.98</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6145.87</v>
+        <v>7948.59</v>
       </c>
       <c r="C5" t="n">
-        <v>6145.87</v>
+        <v>7948.59</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4040.33</v>
+        <v>4875.33</v>
       </c>
       <c r="C6" t="n">
-        <v>4040.33</v>
+        <v>4875.33</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1551.77</v>
+        <v>2024.36</v>
       </c>
       <c r="C7" t="n">
-        <v>1551.77</v>
+        <v>2024.36</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1519.54</v>
+        <v>1896.2</v>
       </c>
       <c r="C8" t="n">
-        <v>1519.54</v>
+        <v>1896.2</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22792.34</v>
+        <v>28359.03</v>
       </c>
       <c r="C9" t="n">
-        <v>22792.34</v>
+        <v>28359.03</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-03</t>
+          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-04</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5989.57</v>
+        <v>7403.53</v>
       </c>
       <c r="C3" t="n">
-        <v>5989.57</v>
+        <v>7403.53</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5624.98</v>
+        <v>6009.1</v>
       </c>
       <c r="C4" t="n">
-        <v>5624.98</v>
+        <v>6009.1</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7948.59</v>
+        <v>9825.879999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>7948.59</v>
+        <v>9825.879999999999</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4875.33</v>
+        <v>5768.75</v>
       </c>
       <c r="C6" t="n">
-        <v>4875.33</v>
+        <v>5768.75</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2024.36</v>
+        <v>2414.67</v>
       </c>
       <c r="C7" t="n">
-        <v>2024.36</v>
+        <v>2414.67</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1896.2</v>
+        <v>2277.27</v>
       </c>
       <c r="C8" t="n">
-        <v>1896.2</v>
+        <v>2277.27</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>28359.03</v>
+        <v>33699.2</v>
       </c>
       <c r="C9" t="n">
-        <v>28359.03</v>
+        <v>33699.2</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-04</t>
+          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-05</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7403.53</v>
+        <v>9604.83</v>
       </c>
       <c r="C3" t="n">
-        <v>7403.53</v>
+        <v>9604.83</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6009.1</v>
+        <v>6785.31</v>
       </c>
       <c r="C4" t="n">
-        <v>6009.1</v>
+        <v>6785.31</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9825.879999999999</v>
+        <v>12054.37</v>
       </c>
       <c r="C5" t="n">
-        <v>9825.879999999999</v>
+        <v>12054.37</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5768.75</v>
+        <v>7448.71</v>
       </c>
       <c r="C6" t="n">
-        <v>5768.75</v>
+        <v>7448.71</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2414.67</v>
+        <v>2802.74</v>
       </c>
       <c r="C7" t="n">
-        <v>2414.67</v>
+        <v>2802.74</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2277.27</v>
+        <v>3146.22</v>
       </c>
       <c r="C8" t="n">
-        <v>2277.27</v>
+        <v>3146.22</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>33699.2</v>
+        <v>41842.18</v>
       </c>
       <c r="C9" t="n">
-        <v>33699.2</v>
+        <v>41842.18</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-05</t>
+          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-06</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9604.83</v>
+        <v>13876.94</v>
       </c>
       <c r="C3" t="n">
-        <v>9604.83</v>
+        <v>13876.94</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6785.31</v>
+        <v>12027.33</v>
       </c>
       <c r="C4" t="n">
-        <v>6785.31</v>
+        <v>12027.33</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12054.37</v>
+        <v>16265.81</v>
       </c>
       <c r="C5" t="n">
-        <v>12054.37</v>
+        <v>16265.81</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7448.71</v>
+        <v>10872.97</v>
       </c>
       <c r="C6" t="n">
-        <v>7448.71</v>
+        <v>10872.97</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2802.74</v>
+        <v>3548.46</v>
       </c>
       <c r="C7" t="n">
-        <v>2802.74</v>
+        <v>3548.46</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3146.22</v>
+        <v>4726.07</v>
       </c>
       <c r="C8" t="n">
-        <v>3146.22</v>
+        <v>4726.07</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>41842.18</v>
+        <v>61317.58</v>
       </c>
       <c r="C9" t="n">
-        <v>41842.18</v>
+        <v>61317.58</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-06</t>
+          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-07</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13876.94</v>
+        <v>17196.96</v>
       </c>
       <c r="C3" t="n">
-        <v>13876.94</v>
+        <v>17196.96</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12027.33</v>
+        <v>14713.04</v>
       </c>
       <c r="C4" t="n">
-        <v>12027.33</v>
+        <v>14713.04</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16265.81</v>
+        <v>19868.01</v>
       </c>
       <c r="C5" t="n">
-        <v>16265.81</v>
+        <v>19868.01</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10872.97</v>
+        <v>12845.5</v>
       </c>
       <c r="C6" t="n">
-        <v>10872.97</v>
+        <v>12845.5</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3548.46</v>
+        <v>4024.64</v>
       </c>
       <c r="C7" t="n">
-        <v>3548.46</v>
+        <v>4024.64</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4726.07</v>
+        <v>5827.87</v>
       </c>
       <c r="C8" t="n">
-        <v>4726.07</v>
+        <v>5827.87</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>61317.58</v>
+        <v>74476.01999999999</v>
       </c>
       <c r="C9" t="n">
-        <v>61317.58</v>
+        <v>74476.01999999999</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-07</t>
+          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-08</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17196.96</v>
+        <v>18654.92</v>
       </c>
       <c r="C3" t="n">
-        <v>17196.96</v>
+        <v>18654.92</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14713.04</v>
+        <v>15433.58</v>
       </c>
       <c r="C4" t="n">
-        <v>14713.04</v>
+        <v>15433.58</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19868.01</v>
+        <v>21840.5</v>
       </c>
       <c r="C5" t="n">
-        <v>19868.01</v>
+        <v>21840.5</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12845.5</v>
+        <v>13365.11</v>
       </c>
       <c r="C6" t="n">
-        <v>12845.5</v>
+        <v>13365.11</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4024.64</v>
+        <v>4395.88</v>
       </c>
       <c r="C7" t="n">
-        <v>4024.64</v>
+        <v>4395.88</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5827.87</v>
+        <v>6073.61</v>
       </c>
       <c r="C8" t="n">
-        <v>5827.87</v>
+        <v>6073.61</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>74476.01999999999</v>
+        <v>79763.60000000001</v>
       </c>
       <c r="C9" t="n">
-        <v>74476.01999999999</v>
+        <v>79763.60000000001</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-08</t>
+          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-09</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18654.92</v>
+        <v>19922.12</v>
       </c>
       <c r="C3" t="n">
-        <v>18654.92</v>
+        <v>19922.12</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15433.58</v>
+        <v>15877.56</v>
       </c>
       <c r="C4" t="n">
-        <v>15433.58</v>
+        <v>15877.56</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21840.5</v>
+        <v>23310.03</v>
       </c>
       <c r="C5" t="n">
-        <v>21840.5</v>
+        <v>23310.03</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13365.11</v>
+        <v>14179.54</v>
       </c>
       <c r="C6" t="n">
-        <v>13365.11</v>
+        <v>14179.54</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4395.88</v>
+        <v>4896.78</v>
       </c>
       <c r="C7" t="n">
-        <v>4395.88</v>
+        <v>4896.78</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6073.61</v>
+        <v>6335.92</v>
       </c>
       <c r="C8" t="n">
-        <v>6073.61</v>
+        <v>6335.92</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>79763.60000000001</v>
+        <v>84521.95</v>
       </c>
       <c r="C9" t="n">
-        <v>79763.60000000001</v>
+        <v>84521.95</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-09</t>
+          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-10</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19922.12</v>
+        <v>21576.07</v>
       </c>
       <c r="C3" t="n">
-        <v>19922.12</v>
+        <v>21576.07</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15877.56</v>
+        <v>16426.24</v>
       </c>
       <c r="C4" t="n">
-        <v>15877.56</v>
+        <v>16426.24</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23310.03</v>
+        <v>25024.61</v>
       </c>
       <c r="C5" t="n">
-        <v>23310.03</v>
+        <v>25024.61</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14179.54</v>
+        <v>14772.01</v>
       </c>
       <c r="C6" t="n">
-        <v>14179.54</v>
+        <v>14772.01</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4896.78</v>
+        <v>5199.9</v>
       </c>
       <c r="C7" t="n">
-        <v>4896.78</v>
+        <v>5199.9</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6335.92</v>
+        <v>6682.05</v>
       </c>
       <c r="C8" t="n">
-        <v>6335.92</v>
+        <v>6682.05</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>84521.95</v>
+        <v>89680.87999999999</v>
       </c>
       <c r="C9" t="n">
-        <v>84521.95</v>
+        <v>89680.87999999999</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-10</t>
+          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-11</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21576.07</v>
+        <v>23232.11</v>
       </c>
       <c r="C3" t="n">
-        <v>21576.07</v>
+        <v>23232.11</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16426.24</v>
+        <v>16897.27</v>
       </c>
       <c r="C4" t="n">
-        <v>16426.24</v>
+        <v>16897.27</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25024.61</v>
+        <v>26982.12</v>
       </c>
       <c r="C5" t="n">
-        <v>25024.61</v>
+        <v>26982.12</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14772.01</v>
+        <v>15835.15</v>
       </c>
       <c r="C6" t="n">
-        <v>14772.01</v>
+        <v>15835.15</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5199.9</v>
+        <v>5594.91</v>
       </c>
       <c r="C7" t="n">
-        <v>5199.9</v>
+        <v>5594.91</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6682.05</v>
+        <v>7063.84</v>
       </c>
       <c r="C8" t="n">
-        <v>6682.05</v>
+        <v>7063.84</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>89680.87999999999</v>
+        <v>95605.39999999999</v>
       </c>
       <c r="C9" t="n">
-        <v>89680.87999999999</v>
+        <v>95605.39999999999</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-11</t>
+          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-12</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23232.11</v>
+        <v>25595.55</v>
       </c>
       <c r="C3" t="n">
-        <v>23232.11</v>
+        <v>25595.55</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16897.27</v>
+        <v>17808.14</v>
       </c>
       <c r="C4" t="n">
-        <v>16897.27</v>
+        <v>17808.14</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26982.12</v>
+        <v>29472.34</v>
       </c>
       <c r="C5" t="n">
-        <v>26982.12</v>
+        <v>29472.34</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15835.15</v>
+        <v>17945.93</v>
       </c>
       <c r="C6" t="n">
-        <v>15835.15</v>
+        <v>17945.93</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5594.91</v>
+        <v>6022.98</v>
       </c>
       <c r="C7" t="n">
-        <v>5594.91</v>
+        <v>6022.98</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7063.84</v>
+        <v>7954.08</v>
       </c>
       <c r="C8" t="n">
-        <v>7063.84</v>
+        <v>7954.08</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>95605.39999999999</v>
+        <v>104799.02</v>
       </c>
       <c r="C9" t="n">
-        <v>95605.39999999999</v>
+        <v>104799.02</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
